--- a/r4-ELGA-IV-Diabetes-dev2/StructureDefinition-iv-condition-diagnose.xlsx
+++ b/r4-ELGA-IV-Diabetes-dev2/StructureDefinition-iv-condition-diagnose.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-13T20:06:34+00:00</t>
+    <t>2025-01-17T09:25:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-IV-Diabetes-dev2/StructureDefinition-iv-condition-diagnose.xlsx
+++ b/r4-ELGA-IV-Diabetes-dev2/StructureDefinition-iv-condition-diagnose.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T09:25:14+00:00</t>
+    <t>2025-01-17T12:03:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-IV-Diabetes-dev2/StructureDefinition-iv-condition-diagnose.xlsx
+++ b/r4-ELGA-IV-Diabetes-dev2/StructureDefinition-iv-condition-diagnose.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T12:03:37+00:00</t>
+    <t>2025-01-20T07:38:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-IV-Diabetes-dev2/StructureDefinition-iv-condition-diagnose.xlsx
+++ b/r4-ELGA-IV-Diabetes-dev2/StructureDefinition-iv-condition-diagnose.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-20T07:38:35+00:00</t>
+    <t>2025-01-20T07:50:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-IV-Diabetes-dev2/StructureDefinition-iv-condition-diagnose.xlsx
+++ b/r4-ELGA-IV-Diabetes-dev2/StructureDefinition-iv-condition-diagnose.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-20T07:50:11+00:00</t>
+    <t>2025-01-21T10:53:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -656,7 +656,7 @@
     <t>0..1 to account for primarily narrative only resources.</t>
   </si>
   <si>
-    <t>https://fhir.hl7.at/elga-iv-diab-r4/ValueSet/vs-allediagnosentest</t>
+    <t>https://diab.iv.elga.gv.at/ValueSet/vs-allediagnosentest</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -1428,7 +1428,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="85.23828125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="58.9375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="51.921875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>
